--- a/docs/starting_docs/04_3일차_팀프로젝트_실습기획서.xlsx
+++ b/docs/starting_docs/04_3일차_팀프로젝트_실습기획서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\workspace\00-startcamp\Day03\vibeproj2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\workspace\00-startcamp\Day03\vibeproj2\docs\starting_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267AE852-7595-4CB5-B2B1-57F35C9E9DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2C320C-8255-459A-83A2-F80502228B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13290" yWindow="3300" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8040" yWindow="3585" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="336">
   <si>
     <t>실습 소재</t>
   </si>
@@ -7382,6 +7382,111 @@
   </si>
   <si>
     <t>외부 API 키가 추가로 필요하고 라이선스 사전 확인 의무(III-1-나) 발생 — 예산·키 범위 초과 위험</t>
+  </si>
+  <si>
+    <t>부울경/경남</t>
+  </si>
+  <si>
+    <t>지역 주민.관광객이 공공데이터에 흩어진 지역정보를 한 곳에서 찾고 공유할 채널이 없음</t>
+  </si>
+  <si>
+    <t>선정 권역 방문 관광객 및 지역 주민 (회원가입 부담 없는 익명 이용자)</t>
+  </si>
+  <si>
+    <t>납기 내 필수기능 100% 구현 + 선택기능 1개 배포 + 배포 URL 정상 동작</t>
+  </si>
+  <si>
+    <t>선정 1개 권역 카테고리 게시판 CRUD (목록/상세/작성/수정/삭제, 비밀번호 기반 권한)</t>
+  </si>
+  <si>
+    <t>챗봇 API(POST /api/chat) 및 채팅 UI (대화 히스토리 유지, 모바일 대응, 플로팅)</t>
+  </si>
+  <si>
+    <t>FE(화면): Vue.js 3 SPA(새로고침 없는 화면전환) / BE(서버): FastAPI + SQLAlchemy(DB 연결 도구) + SQLite(가벼운 데이터베이스)</t>
+  </si>
+  <si>
+    <t>Netlify(FE 배포 서비스).Render(BE 배포 서비스)로 배포 및 URL 동작 확인</t>
+  </si>
+  <si>
+    <t>기능명세서(데이터 출처.라이선스 목록 포함) 및 WBS 문서</t>
+  </si>
+  <si>
+    <t>지도 시각화 - Kakao Maps API로 권역 내 관광지.맛집 위치를 지도에 마커로 표시</t>
+  </si>
+  <si>
+    <t>지도 필터 기능 - 카테고리별(관광지/맛집) 마커 필터링 및 클릭 시 상세정보 팝업</t>
+  </si>
+  <si>
+    <t>권역 소개 페이지 - 선정 권역 개요 및 대표 이미지 노출 (지도 화면 상단)</t>
+  </si>
+  <si>
+    <t>회원가입/로그인, 소셜 인증 등 사용자 계정 체계</t>
+  </si>
+  <si>
+    <t>선정하지 않은 나머지 4개 권역 데이터 및 기능</t>
+  </si>
+  <si>
+    <t>선정하지 않은 나머지 선택기능</t>
+  </si>
+  <si>
+    <t>요구사항 분석 및 확정</t>
+  </si>
+  <si>
+    <t>팀전체</t>
+  </si>
+  <si>
+    <t>예정</t>
+  </si>
+  <si>
+    <t>권역 선정 및 MVP 정의</t>
+  </si>
+  <si>
+    <t>기획팀</t>
+  </si>
+  <si>
+    <t>DB 스키마 설계 (SQLite)</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>API 명세서 작성</t>
+  </si>
+  <si>
+    <t>FE 기본 레이아웃/라우팅</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>BE 게시판 CRUD API</t>
+  </si>
+  <si>
+    <t>FE 게시판 화면 연동</t>
+  </si>
+  <si>
+    <t>챗봇 API 개발</t>
+  </si>
+  <si>
+    <t>챗봇 UI 위젯 개발</t>
+  </si>
+  <si>
+    <t>선택기능 구현(택1)</t>
+  </si>
+  <si>
+    <t>FE/BE</t>
+  </si>
+  <si>
+    <t>Netlify/Render 배포 설정</t>
+  </si>
+  <si>
+    <t>통합 테스트 및 버그 수정</t>
+  </si>
+  <si>
+    <t>기능명세서.데이터출처 정리</t>
+  </si>
+  <si>
+    <t>발표 PPT 제작 및 리허설</t>
   </si>
 </sst>
 </file>
@@ -7391,7 +7496,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;Day &quot;0"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7693,8 +7798,33 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7797,8 +7927,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCADCFC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF028090"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4D6F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E4B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -7919,11 +8091,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -7999,6 +8184,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8054,15 +8275,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -8075,29 +8287,14 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8135,60 +8332,109 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="44" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF028090"/>
           <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8462,10 +8708,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="33"/>
+      <c r="C2" s="45"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -8500,10 +8746,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="30"/>
+      <c r="C9" s="42"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -8554,28 +8800,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="32"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="35"/>
+      <c r="C18" s="47"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="28"/>
+      <c r="C19" s="40"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="28"/>
+      <c r="C20" s="40"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -8609,13 +8855,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -8707,46 +8953,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="30"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="42"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8779,22 +9025,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="30"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -8823,580 +9069,580 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="85" t="s">
+      <c r="C6" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="37" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="83" t="s">
+      <c r="D7" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="83" t="s">
+      <c r="E7" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="F7" s="83" t="s">
+      <c r="F7" s="35" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="D8" s="83" t="s">
+      <c r="D8" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="F8" s="83" t="s">
+      <c r="F8" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="F9" s="83" t="s">
+      <c r="F9" s="35" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="F10" s="83" t="s">
+      <c r="F10" s="35" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="F11" s="83" t="s">
+      <c r="F11" s="35" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="83" t="s">
+      <c r="C12" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="35" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="83" t="s">
+      <c r="D13" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="E13" s="83" t="s">
+      <c r="E13" s="35" t="s">
         <v>201</v>
       </c>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="35" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="D14" s="83" t="s">
+      <c r="D14" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="F14" s="83" t="s">
+      <c r="F14" s="35" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="83" t="s">
+      <c r="C15" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="E15" s="83" t="s">
+      <c r="E15" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="83" t="s">
+      <c r="F15" s="35" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C16" s="83" t="s">
+      <c r="C16" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="83" t="s">
+      <c r="D16" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="E16" s="83" t="s">
+      <c r="E16" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="F16" s="83" t="s">
+      <c r="F16" s="35" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="83" t="s">
+      <c r="D17" s="35" t="s">
         <v>216</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="35" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C18" s="83" t="s">
+      <c r="C18" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="D18" s="83" t="s">
+      <c r="D18" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="E18" s="83" t="s">
+      <c r="E18" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="F18" s="83" t="s">
+      <c r="F18" s="35" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="D19" s="83" t="s">
+      <c r="D19" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="F19" s="83" t="s">
+      <c r="F19" s="35" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="83" t="s">
+      <c r="C20" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="D20" s="83" t="s">
+      <c r="D20" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="F20" s="83" t="s">
+      <c r="F20" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="35" t="s">
         <v>231</v>
       </c>
-      <c r="D21" s="83" t="s">
+      <c r="D21" s="35" t="s">
         <v>232</v>
       </c>
-      <c r="E21" s="83" t="s">
+      <c r="E21" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="F21" s="83" t="s">
+      <c r="F21" s="35" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C22" s="83" t="s">
+      <c r="C22" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="D22" s="83" t="s">
+      <c r="D22" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="E22" s="83" t="s">
+      <c r="E22" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="F22" s="83" t="s">
+      <c r="F22" s="35" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1" thickBot="1">
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C23" s="83" t="s">
+      <c r="C23" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="D23" s="83" t="s">
+      <c r="D23" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="35" t="s">
         <v>240</v>
       </c>
-      <c r="F23" s="83" t="s">
+      <c r="F23" s="35" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="43.5" thickBot="1">
-      <c r="B24" s="86" t="s">
+    <row r="24" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B24" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C24" s="83" t="s">
+      <c r="C24" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="D24" s="83" t="s">
+      <c r="D24" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="E24" s="83" t="s">
+      <c r="E24" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="F24" s="83" t="s">
+      <c r="F24" s="35" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="43.5" thickBot="1">
-      <c r="B25" s="86" t="s">
+    <row r="25" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B25" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="83" t="s">
+      <c r="C25" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="D25" s="83" t="s">
+      <c r="D25" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="E25" s="83" t="s">
+      <c r="E25" s="35" t="s">
         <v>248</v>
       </c>
-      <c r="F25" s="83" t="s">
+      <c r="F25" s="35" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="57.75" thickBot="1">
-      <c r="B26" s="86" t="s">
+    <row r="26" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B26" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C26" s="83" t="s">
+      <c r="C26" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="D26" s="83" t="s">
+      <c r="D26" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="E26" s="83" t="s">
+      <c r="E26" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="F26" s="83" t="s">
+      <c r="F26" s="35" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="43.5" thickBot="1">
-      <c r="B27" s="86" t="s">
+    <row r="27" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B27" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C27" s="83" t="s">
+      <c r="C27" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="D27" s="83" t="s">
+      <c r="D27" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="E27" s="83" t="s">
+      <c r="E27" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="F27" s="83" t="s">
+      <c r="F27" s="35" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="43.5" thickBot="1">
-      <c r="B28" s="86" t="s">
+    <row r="28" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B28" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C28" s="83" t="s">
+      <c r="C28" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="D28" s="83" t="s">
+      <c r="D28" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="E28" s="83" t="s">
+      <c r="E28" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="F28" s="83" t="s">
+      <c r="F28" s="35" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="29.25" thickBot="1">
-      <c r="B29" s="86" t="s">
+    <row r="29" spans="2:6" ht="30.75" thickBot="1">
+      <c r="B29" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="D29" s="83" t="s">
+      <c r="D29" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="F29" s="83" t="s">
+      <c r="F29" s="35" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="43.5" thickBot="1">
-      <c r="B30" s="86" t="s">
+    <row r="30" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B30" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="83" t="s">
+      <c r="C30" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="D30" s="83" t="s">
+      <c r="D30" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="E30" s="83" t="s">
+      <c r="E30" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="F30" s="83" t="s">
+      <c r="F30" s="35" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="100.5" thickBot="1">
-      <c r="B31" s="86" t="s">
+    <row r="31" spans="2:6" ht="105.75" thickBot="1">
+      <c r="B31" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C31" s="83" t="s">
+      <c r="C31" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="D31" s="83" t="s">
+      <c r="D31" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="F31" s="83" t="s">
+      <c r="F31" s="35" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="57.75" thickBot="1">
-      <c r="B32" s="86" t="s">
+    <row r="32" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B32" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C32" s="83" t="s">
+      <c r="C32" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="D32" s="83" t="s">
+      <c r="D32" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="E32" s="83" t="s">
+      <c r="E32" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="F32" s="83" t="s">
+      <c r="F32" s="35" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="100.5" thickBot="1">
-      <c r="B33" s="86" t="s">
+    <row r="33" spans="2:6" ht="105.75" thickBot="1">
+      <c r="B33" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C33" s="83" t="s">
+      <c r="C33" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="D33" s="83" t="s">
+      <c r="D33" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="E33" s="83" t="s">
+      <c r="E33" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="F33" s="83" t="s">
+      <c r="F33" s="35" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="43.5" thickBot="1">
-      <c r="B34" s="86" t="s">
+    <row r="34" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B34" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C34" s="83" t="s">
+      <c r="C34" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="D34" s="83" t="s">
+      <c r="D34" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="E34" s="83" t="s">
+      <c r="E34" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="F34" s="83" t="s">
+      <c r="F34" s="35" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="57.75" thickBot="1">
-      <c r="B35" s="86" t="s">
+    <row r="35" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B35" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C35" s="83" t="s">
+      <c r="C35" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="D35" s="83" t="s">
+      <c r="D35" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="E35" s="83" t="s">
+      <c r="E35" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="F35" s="83" t="s">
+      <c r="F35" s="35" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="43.5" thickBot="1">
-      <c r="B36" s="86" t="s">
+    <row r="36" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B36" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C36" s="83" t="s">
+      <c r="C36" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="D36" s="83" t="s">
+      <c r="D36" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="E36" s="83" t="s">
+      <c r="E36" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="F36" s="83" t="s">
+      <c r="F36" s="35" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="37" spans="2:6" ht="57.75" thickBot="1">
-      <c r="B37" s="86" t="s">
+    <row r="37" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B37" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C37" s="83" t="s">
+      <c r="C37" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="D37" s="83" t="s">
+      <c r="D37" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="E37" s="83" t="s">
+      <c r="E37" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="F37" s="83" t="s">
+      <c r="F37" s="35" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="57.75" thickBot="1">
-      <c r="B38" s="86" t="s">
+    <row r="38" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B38" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C38" s="83" t="s">
+      <c r="C38" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="D38" s="83" t="s">
+      <c r="D38" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="E38" s="83" t="s">
+      <c r="E38" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="F38" s="83" t="s">
+      <c r="F38" s="35" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="57.75" thickBot="1">
-      <c r="B39" s="86" t="s">
+    <row r="39" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B39" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C39" s="83" t="s">
+      <c r="C39" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="D39" s="83" t="s">
+      <c r="D39" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="E39" s="83" t="s">
+      <c r="E39" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="F39" s="83" t="s">
+      <c r="F39" s="35" t="s">
         <v>300</v>
       </c>
     </row>
@@ -9428,37 +9674,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="30"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1" thickBot="1">
       <c r="B5" s="10" t="s">
@@ -9484,186 +9730,186 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="29">
         <v>2</v>
       </c>
-      <c r="E6" s="77">
+      <c r="E6" s="29">
         <v>5</v>
       </c>
-      <c r="F6" s="77">
+      <c r="F6" s="29">
         <v>5</v>
       </c>
-      <c r="G6" s="78">
+      <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="77" t="s">
+      <c r="H6" s="29" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="33">
         <v>2</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="33">
         <v>4</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="33">
         <v>5</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="34">
         <v>40</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="33" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="81">
+      <c r="D8" s="33">
         <v>3</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="33">
         <v>4</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="33">
         <v>4</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="34">
         <v>32</v>
       </c>
-      <c r="H8" s="81" t="s">
+      <c r="H8" s="33" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="81">
+      <c r="D9" s="33">
         <v>3</v>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="33">
         <v>3</v>
       </c>
-      <c r="F9" s="81">
+      <c r="F9" s="33">
         <v>4</v>
       </c>
-      <c r="G9" s="82">
+      <c r="G9" s="34">
         <v>24</v>
       </c>
-      <c r="H9" s="81" t="s">
+      <c r="H9" s="33" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="33">
         <v>3</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="33">
         <v>2</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="33">
         <v>3</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="34">
         <v>12</v>
       </c>
-      <c r="H10" s="81" t="s">
+      <c r="H10" s="33" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="33">
         <v>3</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="33">
         <v>4</v>
       </c>
-      <c r="F11" s="81">
+      <c r="F11" s="33">
         <v>1</v>
       </c>
-      <c r="G11" s="82">
+      <c r="G11" s="34">
         <v>8</v>
       </c>
-      <c r="H11" s="81" t="s">
+      <c r="H11" s="33" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="80" t="s">
+      <c r="C12" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="33">
         <v>2</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="33">
         <v>4</v>
       </c>
-      <c r="F12" s="81">
+      <c r="F12" s="33">
         <v>1</v>
       </c>
-      <c r="G12" s="82">
+      <c r="G12" s="34">
         <v>8</v>
       </c>
-      <c r="H12" s="81" t="s">
+      <c r="H12" s="33" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="33">
         <v>2</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="33">
         <v>2</v>
       </c>
-      <c r="F13" s="81">
+      <c r="F13" s="33">
         <v>2</v>
       </c>
-      <c r="G13" s="82">
+      <c r="G13" s="34">
         <v>8</v>
       </c>
-      <c r="H13" s="81" t="s">
+      <c r="H13" s="33" t="s">
         <v>162</v>
       </c>
     </row>
@@ -9671,12 +9917,12 @@
       <c r="B15" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9706,105 +9952,143 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="39"/>
-    </row>
-    <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="50" t="s">
+      <c r="C2" s="51"/>
+    </row>
+    <row r="3" spans="2:3" ht="18" customHeight="1" thickBot="1">
+      <c r="B3" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="30"/>
-    </row>
-    <row r="4" spans="2:3" ht="30" customHeight="1">
+      <c r="C3" s="42"/>
+    </row>
+    <row r="4" spans="2:3" ht="30" customHeight="1" thickBot="1">
       <c r="B4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="2:3" ht="30" customHeight="1">
+      <c r="C4" s="36" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="30" customHeight="1" thickBot="1">
       <c r="B5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="2:3" ht="30" customHeight="1">
+      <c r="C5" s="87" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="30" customHeight="1" thickBot="1">
       <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="2:3" ht="30" customHeight="1">
+      <c r="C6" s="87" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="30" customHeight="1" thickBot="1">
       <c r="B7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="48" t="s">
+      <c r="C7" s="87" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15" customHeight="1" thickBot="1">
+      <c r="B9" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="49"/>
-    </row>
-    <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="34"/>
-      <c r="C10" s="35"/>
-    </row>
-    <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-    </row>
-    <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-    </row>
-    <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-    </row>
-    <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-    </row>
-    <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="53" t="s">
+      <c r="C9" s="65"/>
+    </row>
+    <row r="10" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B10" s="88" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="89"/>
+    </row>
+    <row r="11" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B11" s="88" t="s">
+        <v>306</v>
+      </c>
+      <c r="C11" s="89"/>
+    </row>
+    <row r="12" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B12" s="90" t="s">
+        <v>307</v>
+      </c>
+      <c r="C12" s="91"/>
+    </row>
+    <row r="13" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B13" s="90" t="s">
+        <v>308</v>
+      </c>
+      <c r="C13" s="91"/>
+    </row>
+    <row r="14" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B14" s="88" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="89"/>
+    </row>
+    <row r="16" spans="2:3" ht="15" customHeight="1" thickBot="1">
+      <c r="B16" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="54"/>
-    </row>
-    <row r="17" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-    </row>
-    <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-    </row>
-    <row r="19" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-    </row>
-    <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="51" t="s">
+      <c r="C16" s="63"/>
+    </row>
+    <row r="17" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B17" s="88" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" s="89"/>
+    </row>
+    <row r="18" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B18" s="88" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" s="89"/>
+    </row>
+    <row r="19" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B19" s="88" t="s">
+        <v>312</v>
+      </c>
+      <c r="C19" s="89"/>
+    </row>
+    <row r="21" spans="2:3" ht="15" customHeight="1" thickBot="1">
+      <c r="B21" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="52"/>
-    </row>
-    <row r="22" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-    </row>
-    <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-    </row>
-    <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
+      <c r="C21" s="61"/>
+    </row>
+    <row r="22" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B22" s="88" t="s">
+        <v>313</v>
+      </c>
+      <c r="C22" s="89"/>
+    </row>
+    <row r="23" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B23" s="88" t="s">
+        <v>314</v>
+      </c>
+      <c r="C23" s="89"/>
+    </row>
+    <row r="24" spans="2:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="B24" s="90" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
@@ -9813,14 +10097,6 @@
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9850,38 +10126,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="79" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="30"/>
-    </row>
-    <row r="4" spans="2:13" ht="25.5" customHeight="1">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="42"/>
+    </row>
+    <row r="4" spans="2:13" ht="25.5" customHeight="1" thickBot="1">
       <c r="B4" s="12" t="s">
         <v>52</v>
       </c>
@@ -9919,356 +10195,523 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="30" customHeight="1">
+    <row r="5" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="str">
-        <f t="shared" ref="H5:H18" si="0">IF(OR(F5="",G5=""),"",G5-F5+1)</f>
-        <v/>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="2:13" ht="30" customHeight="1">
+      <c r="C5" s="92" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="93" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="94" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="95">
+        <v>1</v>
+      </c>
+      <c r="G5" s="95">
+        <v>1</v>
+      </c>
+      <c r="H5" s="94">
+        <v>1</v>
+      </c>
+      <c r="I5" s="94">
+        <v>0</v>
+      </c>
+      <c r="J5" s="94" t="s">
+        <v>318</v>
+      </c>
+      <c r="K5" s="96"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+    </row>
+    <row r="6" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="2:13" ht="30" customHeight="1">
+      <c r="C6" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="99" t="s">
+        <v>319</v>
+      </c>
+      <c r="E6" s="100" t="s">
+        <v>320</v>
+      </c>
+      <c r="F6" s="101">
+        <v>1</v>
+      </c>
+      <c r="G6" s="101">
+        <v>1</v>
+      </c>
+      <c r="H6" s="100">
+        <v>1</v>
+      </c>
+      <c r="I6" s="100">
+        <v>0</v>
+      </c>
+      <c r="J6" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K6" s="102"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+    </row>
+    <row r="7" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="2:13" ht="30" customHeight="1">
+      <c r="C7" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="F7" s="101">
+        <v>1</v>
+      </c>
+      <c r="G7" s="101">
+        <v>1</v>
+      </c>
+      <c r="H7" s="100">
+        <v>1</v>
+      </c>
+      <c r="I7" s="100">
+        <v>0</v>
+      </c>
+      <c r="J7" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K7" s="102"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+    </row>
+    <row r="8" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="2:13" ht="30" customHeight="1">
+      <c r="C8" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="101">
+        <v>1</v>
+      </c>
+      <c r="G8" s="101">
+        <v>1</v>
+      </c>
+      <c r="H8" s="100">
+        <v>1</v>
+      </c>
+      <c r="I8" s="100">
+        <v>0</v>
+      </c>
+      <c r="J8" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K8" s="102"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="103"/>
+    </row>
+    <row r="9" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="2:13" ht="30" customHeight="1">
+      <c r="C9" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="F9" s="101">
+        <v>2</v>
+      </c>
+      <c r="G9" s="101">
+        <v>2</v>
+      </c>
+      <c r="H9" s="100">
+        <v>1</v>
+      </c>
+      <c r="I9" s="100">
+        <v>0</v>
+      </c>
+      <c r="J9" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K9" s="103"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="103"/>
+    </row>
+    <row r="10" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B10" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="2:13" ht="30" customHeight="1">
+      <c r="C10" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="F10" s="101">
+        <v>2</v>
+      </c>
+      <c r="G10" s="101">
+        <v>2</v>
+      </c>
+      <c r="H10" s="100">
+        <v>1</v>
+      </c>
+      <c r="I10" s="100">
+        <v>0</v>
+      </c>
+      <c r="J10" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K10" s="103"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="103"/>
+    </row>
+    <row r="11" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="2:13" ht="30" customHeight="1">
+      <c r="C11" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="F11" s="101">
+        <v>2</v>
+      </c>
+      <c r="G11" s="101">
+        <v>2</v>
+      </c>
+      <c r="H11" s="100">
+        <v>1</v>
+      </c>
+      <c r="I11" s="100">
+        <v>0</v>
+      </c>
+      <c r="J11" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K11" s="103"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="103"/>
+    </row>
+    <row r="12" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="2:13" ht="30" customHeight="1">
+      <c r="C12" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="99" t="s">
+        <v>328</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="F12" s="101">
+        <v>2</v>
+      </c>
+      <c r="G12" s="101">
+        <v>2</v>
+      </c>
+      <c r="H12" s="100">
+        <v>1</v>
+      </c>
+      <c r="I12" s="100">
+        <v>0</v>
+      </c>
+      <c r="J12" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K12" s="103"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103"/>
+    </row>
+    <row r="13" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="2:13" ht="30" customHeight="1">
+      <c r="C13" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="99" t="s">
+        <v>329</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="F13" s="101">
+        <v>2</v>
+      </c>
+      <c r="G13" s="101">
+        <v>2</v>
+      </c>
+      <c r="H13" s="100">
+        <v>1</v>
+      </c>
+      <c r="I13" s="100">
+        <v>0</v>
+      </c>
+      <c r="J13" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K13" s="103"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="103"/>
+    </row>
+    <row r="14" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="2:13" ht="30" customHeight="1">
+      <c r="C14" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="F14" s="101">
+        <v>2</v>
+      </c>
+      <c r="G14" s="101">
+        <v>2</v>
+      </c>
+      <c r="H14" s="100">
+        <v>1</v>
+      </c>
+      <c r="I14" s="100">
+        <v>0</v>
+      </c>
+      <c r="J14" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K14" s="103"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="103"/>
+    </row>
+    <row r="15" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="2:13" ht="30" customHeight="1">
+      <c r="C15" s="106" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="F15" s="101">
+        <v>3</v>
+      </c>
+      <c r="G15" s="101">
+        <v>3</v>
+      </c>
+      <c r="H15" s="100">
+        <v>1</v>
+      </c>
+      <c r="I15" s="100">
+        <v>0</v>
+      </c>
+      <c r="J15" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K15" s="103"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="102"/>
+    </row>
+    <row r="16" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B16" s="5">
         <v>12</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="2:13" ht="30" customHeight="1">
+      <c r="C16" s="107" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="99" t="s">
+        <v>333</v>
+      </c>
+      <c r="E16" s="100" t="s">
+        <v>317</v>
+      </c>
+      <c r="F16" s="101">
+        <v>3</v>
+      </c>
+      <c r="G16" s="101">
+        <v>3</v>
+      </c>
+      <c r="H16" s="100">
+        <v>1</v>
+      </c>
+      <c r="I16" s="100">
+        <v>0</v>
+      </c>
+      <c r="J16" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K16" s="103"/>
+      <c r="L16" s="103"/>
+      <c r="M16" s="102"/>
+    </row>
+    <row r="17" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B17" s="5">
         <v>13</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="2:13" ht="30" customHeight="1">
+      <c r="C17" s="108" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="99" t="s">
+        <v>334</v>
+      </c>
+      <c r="E17" s="100" t="s">
+        <v>320</v>
+      </c>
+      <c r="F17" s="101">
+        <v>3</v>
+      </c>
+      <c r="G17" s="101">
+        <v>3</v>
+      </c>
+      <c r="H17" s="100">
+        <v>1</v>
+      </c>
+      <c r="I17" s="100">
+        <v>0</v>
+      </c>
+      <c r="J17" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K17" s="103"/>
+      <c r="L17" s="103"/>
+      <c r="M17" s="102"/>
+    </row>
+    <row r="18" spans="2:13" ht="30" customHeight="1" thickBot="1">
       <c r="B18" s="5">
         <v>14</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="C18" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="99" t="s">
+        <v>335</v>
+      </c>
+      <c r="E18" s="100" t="s">
+        <v>317</v>
+      </c>
+      <c r="F18" s="101">
+        <v>3</v>
+      </c>
+      <c r="G18" s="101">
+        <v>3</v>
+      </c>
+      <c r="H18" s="100">
+        <v>1</v>
+      </c>
+      <c r="I18" s="100">
+        <v>0</v>
+      </c>
+      <c r="J18" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="102"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="82"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="60"/>
+      <c r="C21" s="84"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="62"/>
+      <c r="C22" s="86"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="66"/>
+      <c r="C23" s="70"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="68"/>
+      <c r="C24" s="72"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="74"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="72"/>
+      <c r="C26" s="76"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="74"/>
+      <c r="C27" s="78"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="64"/>
+      <c r="C28" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
-  <conditionalFormatting sqref="K5:M18">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C5:C18" xr:uid="{00000000-0002-0000-0500-000000000000}">
-      <formula1>"기획,설계,개발,배포,테스트,문서화,발표준비"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J5:J18" xr:uid="{00000000-0002-0000-0500-000001000000}">
-      <formula1>"예정,진행중,완료"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -10288,16 +10731,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="39"/>
+      <c r="C2" s="51"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="30"/>
+      <c r="C3" s="42"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">
